--- a/DotNetExcel/StarkBankExcel/StarkBank.xlsx
+++ b/DotNetExcel/StarkBankExcel/StarkBank.xlsx
@@ -1,44 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stark - Admin\Starkbank-Code\Git-Excel\DotNetExcel\StarkBankExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F858E87-BBF2-49E0-9AAD-DA5E23035A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92461A04-B7EC-4E53-8A75-006D6400DB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="15375" windowHeight="7785" firstSheet="1" activeTab="1" xr2:uid="{DD233689-9B57-48BF-9576-9FA43391D3F3}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="7785" firstSheet="16" activeTab="16" xr2:uid="{DD233689-9B57-48BF-9576-9FA43391D3F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="Principal" sheetId="1" r:id="rId2"/>
     <sheet name="Solicitar Cartões Físicos" sheetId="18" r:id="rId3"/>
-    <sheet name="Compras Cartão" sheetId="12" r:id="rId4"/>
-    <sheet name="Extrato Cartão" sheetId="11" r:id="rId5"/>
-    <sheet name="Extrato" sheetId="7" r:id="rId6"/>
-    <sheet name="Consulta de Transferencias" sheetId="17" r:id="rId7"/>
-    <sheet name="Transferências Com Aprovação" sheetId="4" r:id="rId8"/>
-    <sheet name="Consulta de Aprovações" sheetId="15" r:id="rId9"/>
-    <sheet name="Consulta de Chaves Pix" sheetId="3" r:id="rId10"/>
-    <sheet name="Consulta de Boletos Emitidos" sheetId="8" r:id="rId11"/>
-    <sheet name="Pagamento de Boleto" sheetId="16" r:id="rId12"/>
-    <sheet name="Historico pagamento de Boletos" sheetId="14" r:id="rId13"/>
-    <sheet name="Histórico de Boletos Emitido" sheetId="9" r:id="rId14"/>
-    <sheet name="Consulta de Invoice Emitidas" sheetId="6" r:id="rId15"/>
-    <sheet name="Reversão de invoice" sheetId="13" r:id="rId16"/>
-    <sheet name="Emissão de Boleto" sheetId="10" r:id="rId17"/>
-    <sheet name="Emissão de Invoice Pix" sheetId="5" r:id="rId18"/>
+    <sheet name="Split Receiver" sheetId="19" r:id="rId4"/>
+    <sheet name="Split Consultas" sheetId="20" r:id="rId5"/>
+    <sheet name="Compras Cartão" sheetId="12" r:id="rId6"/>
+    <sheet name="Extrato Cartão" sheetId="11" r:id="rId7"/>
+    <sheet name="Extrato" sheetId="7" r:id="rId8"/>
+    <sheet name="Consulta de Transferencias" sheetId="17" r:id="rId9"/>
+    <sheet name="Transferências Com Aprovação" sheetId="4" r:id="rId10"/>
+    <sheet name="Consulta de Aprovações" sheetId="15" r:id="rId11"/>
+    <sheet name="Consulta de Chaves Pix" sheetId="3" r:id="rId12"/>
+    <sheet name="Consulta de Boletos Emitidos" sheetId="8" r:id="rId13"/>
+    <sheet name="Pagamento de Boleto" sheetId="16" r:id="rId14"/>
+    <sheet name="Historico pagamento de Boletos" sheetId="14" r:id="rId15"/>
+    <sheet name="Histórico de Boletos Emitido" sheetId="9" r:id="rId16"/>
+    <sheet name="Consulta de Invoice Emitidas" sheetId="6" r:id="rId17"/>
+    <sheet name="Reversão de invoice" sheetId="13" r:id="rId18"/>
+    <sheet name="Emissão de Boleto" sheetId="10" r:id="rId19"/>
+    <sheet name="Emissão de Invoice Pix" sheetId="5" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Consulta de Boletos Emitidos'!$A$9:$V$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Consulta de Chaves Pix'!$A$9:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Emissão de Invoice Pix'!$A$9:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Extrato!$A$9:$I$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Histórico de Boletos Emitido'!$A$9:$V$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Transferências Com Aprovação'!$A$9:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Consulta de Boletos Emitidos'!$A$9:$V$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Consulta de Chaves Pix'!$A$9:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Emissão de Invoice Pix'!$A$9:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Extrato!$A$9:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Histórico de Boletos Emitido'!$A$9:$V$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Transferências Com Aprovação'!$A$9:$J$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="123">
   <si>
     <t>Chave Pix</t>
   </si>
@@ -407,6 +409,30 @@
   <si>
     <t>Stark Bank SDK Excel - v3.0.5</t>
   </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>ID da Invoice</t>
+  </si>
+  <si>
+    <t>Seller</t>
+  </si>
+  <si>
+    <t>Split</t>
+  </si>
+  <si>
+    <t>Split 1</t>
+  </si>
+  <si>
+    <t>Split 2</t>
+  </si>
+  <si>
+    <t>Split 3</t>
+  </si>
 </sst>
 </file>
 
@@ -827,14 +853,14 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="43935BDA7439194471449D234CFD527D9886B4"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="61C193B816E9F46402B69E486951268B9D43F6"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1588"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -844,14 +870,14 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5FE4E9EDE5117D54C395AB0B52D849B4179075"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="52AAAB8D657270547E35903054721DD6D95665"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -878,6 +904,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="312CEA5A03E075348FD390B53D647C6AC80183"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX21.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="42B7BCE474DE9244FC448DC747BAF246C6B6F4"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX22.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="8EEE883E98B9308405B896878CAE4FED0F1298"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1561"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX23.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="73666E11F7836274C397B0297910A673B5FC77"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="63FBECDCF6DD67640326A5166B97042280E116"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="50F84147154B2F5405C5BC645A717138154775"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="43935BDA7439194471449D234CFD527D9886B4"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5FE4E9EDE5117D54C395AB0B52D849B4179075"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="690DE6C82662BD648A469A3C645736EF297746"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -890,7 +1052,7 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -903,142 +1065,6 @@
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
   <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX22.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="80815DC5B82C3B8498489E26894C5C52875E28"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3757"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1588"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX23.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="75E9B6F4C78CB974E3679B0970BD37E29B8E77"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3201"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4DD8155564BBBB442F449A794155F293DF1F94"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="576D85FB2525B8547055A14351ED593B73E215"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3201"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="6D72D142762FA7648186B99160B384DA4EEAD6"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="17FA434AF19D0F14BB3186971AC86AABFB7FD1"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="21156A5D42671D24110290D22610E26CEF0122"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="36BF4D76D36CAA346A9392633D35C8E7F4F293"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -1065,6 +1091,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="80815DC5B82C3B8498489E26894C5C52875E28"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3757"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1588"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX31.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="75E9B6F4C78CB974E3679B0970BD37E29B8E77"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3201"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX32.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4DD8155564BBBB442F449A794155F293DF1F94"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="576D85FB2525B8547055A14351ED593B73E215"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3201"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="6D72D142762FA7648186B99160B384DA4EEAD6"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX35.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="17FA434AF19D0F14BB3186971AC86AABFB7FD1"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX36.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="21156A5D42671D24110290D22610E26CEF0122"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX37.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="36BF4D76D36CAA346A9392633D35C8E7F4F293"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX38.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="4BDD5BFBC494C944E75484BA43B9AFC575EDE4"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -1077,7 +1239,7 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX39.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1090,142 +1252,6 @@
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
   <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX32.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3AA2985733B4083434D3B3DA395B83B5AB5FB3"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="29E4B6D5F2B5EF24B732AC612476A095FC12F2"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1BF3F766D1EC8E14D641AB8818D8695A960D41"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX35.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="6EAFFE9C06D4276431A6BB2F6072D3CF2C1786"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX36.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="7C9BBDE4E751B574F557BC077FC280926F0487"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX37.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1D3C8440119274147F5190E81CB29314F1A0B1"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX38.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2F27997732C2CB2441C298BB24A21C18565F42"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX39.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="32D5429B8373DD34ED03A9043941F439C19723"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -1252,6 +1278,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3AA2985733B4083434D3B3DA395B83B5AB5FB3"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX41.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="29E4B6D5F2B5EF24B732AC612476A095FC12F2"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX42.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1BF3F766D1EC8E14D641AB8818D8695A960D41"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX43.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="6EAFFE9C06D4276431A6BB2F6072D3CF2C1786"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX44.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="7C9BBDE4E751B574F557BC077FC280926F0487"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX45.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1D3C8440119274147F5190E81CB29314F1A0B1"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX46.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2F27997732C2CB2441C298BB24A21C18565F42"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX47.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="32D5429B8373DD34ED03A9043941F439C19723"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX48.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="4725C0A2E4AB894430D4AEF74EE21D1AD6A734"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -1264,148 +1426,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX49.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="5F3C3A5AA5DBB654AFD5A7C25896612CBE6DC5"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX42.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="6D5513A176D11B6489268BF06C26AC9C7986A6"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX43.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="7B414461476FE874FCC7AF487111D4DE5C31F7"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX44.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="8A681C04683975842508B2258073BEA1C60FD8"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX45.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="9C5D0F81D9A7DC9451D986E29349E294E0E0F9"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX46.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="6DF62D0586063D64B576813E624CB2DFF23CB6"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3334"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1217"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX47.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="581AFF66D5395E54CBC5BEBA52A895EF8D96F5"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX48.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4EDC5AE2D4725F442D54BDB348E5FBB86B52C4"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX49.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3443F6D933A917348513994830A35447867593"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1439,6 +1465,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="6D5513A176D11B6489268BF06C26AC9C7986A6"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX51.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="7B414461476FE874FCC7AF487111D4DE5C31F7"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX52.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="8A681C04683975842508B2258073BEA1C60FD8"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX53.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="9C5D0F81D9A7DC9451D986E29349E294E0E0F9"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX54.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="6DF62D0586063D64B576813E624CB2DFF23CB6"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3334"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1217"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX55.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="581AFF66D5395E54CBC5BEBA52A895EF8D96F5"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX56.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4EDC5AE2D4725F442D54BDB348E5FBB86B52C4"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX57.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3443F6D933A917348513994830A35447867593"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX58.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="2F31A0EA52B80A243F02887A226A80BA2346A2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -1451,7 +1613,7 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX59.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1464,142 +1626,6 @@
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="3096"/>
   <ax:ocxPr ax:name="Sizel_cy" ax:value="1244"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX52.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="55583C5835971E5409E5944455073F47DDC2A5"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX53.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="43443F65340DC5448034B84249A78BF6899C14"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX54.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="393B0D4DB376B1348C53AA283ED005A8E39383"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX55.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2FAFF23AA2246924D782B58F21CB01DE2B8C82"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX56.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="192AED9321906F1430518AA91C61F691A49AE1"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX57.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="64B7B760262CDD643836A79A641DDB36424F16"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX58.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="180E934D715B35148521A4DA16BAC3E49AA421"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX59.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="209AD430929B0C246352BB46205966BBA32BE2"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -1626,6 +1652,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="55583C5835971E5409E5944455073F47DDC2A5"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX61.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="43443F65340DC5448034B84249A78BF6899C14"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX62.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="393B0D4DB376B1348C53AA283ED005A8E39383"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX63.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2FAFF23AA2246924D782B58F21CB01DE2B8C82"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX64.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="192AED9321906F1430518AA91C61F691A49AE1"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX65.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="64B7B760262CDD643836A79A641DDB36424F16"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX66.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="180E934D715B35148521A4DA16BAC3E49AA421"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX67.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="209AD430929B0C246352BB46205966BBA32BE2"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX68.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="340115F7C331F8342C23902032B2E1FE922923"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -1638,7 +1800,7 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX69.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1651,142 +1813,6 @@
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
   <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX62.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1FF48C76A17A8C14A1D1B461189CB6BA129791"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX63.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="23587ECD629DA1245032AC232F0D6B45106E92"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX64.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3B4BCFBAF3A04D341103B77B32A7026959A7C3"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX65.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4F2081B3648833443864BB8143FD2C02F9E634"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX66.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5FCC13B9257A75548E65A9E458AA0E6A413BF5"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX67.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5B4A34D975B853543985A7E75523690B60EC35"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX68.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="42576A9D548EA54490F4BA2045852D9EEA0264"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX69.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="32381B0E43363B340003842439CB6D4833D8F3"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -1813,6 +1839,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1FF48C76A17A8C14A1D1B461189CB6BA129791"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX71.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="23587ECD629DA1245032AC232F0D6B45106E92"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX72.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3B4BCFBAF3A04D341103B77B32A7026959A7C3"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX73.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4F2081B3648833443864BB8143FD2C02F9E634"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX74.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5FCC13B9257A75548E65A9E458AA0E6A413BF5"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX75.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5B4A34D975B853543985A7E75523690B60EC35"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX76.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="42576A9D548EA54490F4BA2045852D9EEA0264"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX77.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="32381B0E43363B340003842439CB6D4833D8F3"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX78.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="207D2713820AB8246622A7CD26A57A9DCA2162"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -1825,148 +1987,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX79.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="19726D3BD1AD01142191B2C41B5B2D13E650B1"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX72.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1B7A977A61ADF41453E1BBBE1183429619DB11"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3281"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX73.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="232EEE2C927B21244D728DA228DC1AAB22C9E2"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX74.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="39558BA7531D2E3412138D1638E54A9A444C63"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX75.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4E23FE0EC4C93C4470948DA849AEEC73F9C744"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX76.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="51A95A66553942547D759A7153A00908FCA885"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX77.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5B4126E875ABC55427F5B28E55218522354BA5"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX78.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="43953CE6E45013447B8491244183EC3B869614"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3149"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX79.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="33A9EADB835964348083B921335A9469D78A13"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2000,6 +2026,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1B7A977A61ADF41453E1BBBE1183429619DB11"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3281"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX81.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="232EEE2C927B21244D728DA228DC1AAB22C9E2"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX82.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="39558BA7531D2E3412138D1638E54A9A444C63"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX83.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4E23FE0EC4C93C4470948DA849AEEC73F9C744"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX84.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="51A95A66553942547D759A7153A00908FCA885"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX85.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5B4126E875ABC55427F5B28E55218522354BA5"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX86.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="43953CE6E45013447B8491244183EC3B869614"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3149"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX87.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="33A9EADB835964348083B921335A9469D78A13"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX88.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="245B62680258F8244B928BF02F0D73C394B3A2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -2012,148 +2174,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX89.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="632A921A961CC6648D5697386AA1DF460A0236"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX82.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="482B56B2D4F09144EA9495AD4E1391B3ADA544"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX83.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3C148BBC83328034CB4383F53575DFC2E2D673"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX84.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2DE4C20F929D4D245012850329872D57BE1542"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX85.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1441CBD291E7921466418469122C7CFF2CD931"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX86.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="676BBF00A6812B64BBB6BA716DB953807A8EA6"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX87.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="560AC6FB15F17754F6558A0F58035E0AF7ED85"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX88.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="423CD9C0343555445FB48C9D4CF7D65D1F3284"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX89.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3980FC20730620345FE3A45431A52DCB072F13"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2187,6 +2213,142 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="482B56B2D4F09144EA9495AD4E1391B3ADA544"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX91.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3C148BBC83328034CB4383F53575DFC2E2D673"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX92.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2DE4C20F929D4D245012850329872D57BE1542"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX93.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1441CBD291E7921466418469122C7CFF2CD931"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX94.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="676BBF00A6812B64BBB6BA716DB953807A8EA6"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX95.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="560AC6FB15F17754F6558A0F58035E0AF7ED85"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX96.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="423CD9C0343555445FB48C9D4CF7D65D1F3284"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX97.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3980FC20730620345FE3A45431A52DCB072F13"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX98.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="2596667A2285C4241122B3CF25CD7B218043C2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -2199,7 +2361,7 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX99.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -3033,6 +3195,636 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>495300</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>133350</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="59398" name="_ActiveXWrapper1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s59398"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000006E80000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>800100</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="59399" name="_ActiveXWrapper2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s59399"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000007E80000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>485775</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>695325</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="59400" name="_ActiveXWrapper3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s59400"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000008E80000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>95250</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>647700</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="59401" name="_ActiveXWrapper4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s59401"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000009E80000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>38100</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>542925</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3073" name="_ActiveXWrapper1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-0000010C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>561975</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>295275</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3074" name="_ActiveXWrapper2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-0000020C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>28575</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>123825</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3075" name="_ActiveXWrapper7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-0000030C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>723900</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>123825</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>457200</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3076" name="_ActiveXWrapper8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-0000040C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>123825</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>276225</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3077" name="_ActiveXWrapper5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-0000050C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>714375</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>485775</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3078" name="_ActiveXWrapper6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-0000060C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>3</xdr:row>
@@ -3052,7 +3844,7 @@
                   <a14:compatExt spid="_x0000_s16385"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000001400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000001400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3114,7 +3906,7 @@
                   <a14:compatExt spid="_x0000_s16386"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000002400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000002400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3176,7 +3968,7 @@
                   <a14:compatExt spid="_x0000_s16387"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000003400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000003400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3238,7 +4030,7 @@
                   <a14:compatExt spid="_x0000_s16388"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000004400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000004400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3300,7 +4092,7 @@
                   <a14:compatExt spid="_x0000_s16389"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000005400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000005400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3362,7 +4154,7 @@
                   <a14:compatExt spid="_x0000_s16390"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000006400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000006400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3404,7 +4196,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -3429,7 +4221,7 @@
                   <a14:compatExt spid="_x0000_s73729"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000001200100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000001200100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3491,7 +4283,7 @@
                   <a14:compatExt spid="_x0000_s73730"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000002200100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000002200100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3553,7 +4345,7 @@
                   <a14:compatExt spid="_x0000_s73731"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000003200100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000003200100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3615,7 +4407,7 @@
                   <a14:compatExt spid="_x0000_s73732"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000004200100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000004200100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3657,7 +4449,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -3682,7 +4474,7 @@
                   <a14:compatExt spid="_x0000_s52225"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000001CC0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000001CC0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3744,7 +4536,7 @@
                   <a14:compatExt spid="_x0000_s52226"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000002CC0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000002CC0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3806,7 +4598,7 @@
                   <a14:compatExt spid="_x0000_s52227"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000003CC0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000003CC0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3868,7 +4660,7 @@
                   <a14:compatExt spid="_x0000_s52228"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000004CC0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000004CC0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3930,7 +4722,7 @@
                   <a14:compatExt spid="_x0000_s52229"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000005CC0000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000005CC0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3972,7 +4764,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -3997,7 +4789,7 @@
                   <a14:compatExt spid="_x0000_s20481"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000001500000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000001500000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4059,7 +4851,7 @@
                   <a14:compatExt spid="_x0000_s20482"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000002500000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000002500000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4121,7 +4913,7 @@
                   <a14:compatExt spid="_x0000_s20483"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000003500000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000003500000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4183,7 +4975,7 @@
                   <a14:compatExt spid="_x0000_s20484"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000004500000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000004500000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4245,7 +5037,7 @@
                   <a14:compatExt spid="_x0000_s20485"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000005500000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000005500000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4287,7 +5079,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -4312,7 +5104,7 @@
                   <a14:compatExt spid="_x0000_s8193"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000001200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000001200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4374,7 +5166,7 @@
                   <a14:compatExt spid="_x0000_s8194"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000002200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000002200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4436,7 +5228,7 @@
                   <a14:compatExt spid="_x0000_s8195"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000003200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000003200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4498,7 +5290,7 @@
                   <a14:compatExt spid="_x0000_s8196"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000004200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000004200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4560,7 +5352,7 @@
                   <a14:compatExt spid="_x0000_s8197"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000005200000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000005200000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4602,7 +5394,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -4627,7 +5419,7 @@
                   <a14:compatExt spid="_x0000_s49154"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000002C00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000002C00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4689,7 +5481,7 @@
                   <a14:compatExt spid="_x0000_s49155"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000003C00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000003C00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4751,7 +5543,7 @@
                   <a14:compatExt spid="_x0000_s49156"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000004C00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000004C00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4813,7 +5605,7 @@
                   <a14:compatExt spid="_x0000_s49157"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000005C00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000005C00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4875,7 +5667,7 @@
                   <a14:compatExt spid="_x0000_s49158"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000006C00000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000006C00000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4917,7 +5709,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -4942,7 +5734,7 @@
                   <a14:compatExt spid="_x0000_s24577"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000001600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000001600000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5004,7 +5796,7 @@
                   <a14:compatExt spid="_x0000_s24578"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000002600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000002600000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5066,7 +5858,7 @@
                   <a14:compatExt spid="_x0000_s24579"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000003600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000003600000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5128,7 +5920,7 @@
                   <a14:compatExt spid="_x0000_s24580"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000004600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000004600000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5190,7 +5982,7 @@
                   <a14:compatExt spid="_x0000_s24582"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000006600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000006600000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5232,7 +6024,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -5257,7 +6049,7 @@
                   <a14:compatExt spid="_x0000_s6145"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000001180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000001180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5319,7 +6111,7 @@
                   <a14:compatExt spid="_x0000_s6146"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000002180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000002180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5381,7 +6173,7 @@
                   <a14:compatExt spid="_x0000_s6147"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000003180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000003180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5443,7 +6235,7 @@
                   <a14:compatExt spid="_x0000_s6148"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000004180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000004180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5505,7 +6297,7 @@
                   <a14:compatExt spid="_x0000_s6149"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000005180000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000005180000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5807,6 +6599,512 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
+          <xdr:colOff>1533525</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>142875</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>1171575</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>161925</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="112643" name="_ActiveXWrapper1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s112643"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003B80100}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>1533525</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>1171575</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="112644" name="_ActiveXWrapper2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s112644"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004B80100}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>1238250</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>38101</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>790575</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>57151</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="112645" name="_ActiveXWrapper3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s112645"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F5D709-CEEC-F382-F127-4DD83852F410}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>838200</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>47626</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>1276350</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>47626</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="112646" name="_ActiveXWrapper4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s112646"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D8EE63-C420-2E41-A9A4-08488FD44535}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1381125</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>104775</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>933450</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>123825</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="130053" name="_ActiveXWrapper1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s130053"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{489F1BD4-3E04-E03B-02CF-4CC1B67F9625}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>1381125</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>933450</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="130054" name="_ActiveXWrapper2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s130054"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E54C84C0-8816-BA5D-7025-00C1A8D2C6B0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>1000125</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>57150</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>819150</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="130055" name="_ActiveXWrapper3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s130055"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03441E3D-E676-D0D7-DBDD-A45912D2C778}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>866775</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>66676</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>1066800</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>57150</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="130056" name="_ActiveXWrapper4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s130056"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE7B833F-F6EA-2EC9-E2E5-80661824228B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
           <xdr:colOff>1019175</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>104775</xdr:rowOff>
@@ -5825,7 +7123,7 @@
                   <a14:compatExt spid="_x0000_s37892"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004940000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004940000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5887,7 +7185,7 @@
                   <a14:compatExt spid="_x0000_s37893"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005940000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000005940000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5949,7 +7247,7 @@
                   <a14:compatExt spid="_x0000_s37894"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006940000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000006940000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6011,7 +7309,7 @@
                   <a14:compatExt spid="_x0000_s37895"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007940000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000007940000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6073,7 +7371,7 @@
                   <a14:compatExt spid="_x0000_s37896"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008940000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000008940000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6115,7 +7413,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -6140,7 +7438,7 @@
                   <a14:compatExt spid="_x0000_s28676"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004700000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004700000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6202,7 +7500,7 @@
                   <a14:compatExt spid="_x0000_s28677"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000005700000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005700000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6264,7 +7562,7 @@
                   <a14:compatExt spid="_x0000_s28678"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000006700000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006700000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6326,7 +7624,7 @@
                   <a14:compatExt spid="_x0000_s28679"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000007700000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007700000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6368,7 +7666,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -6393,7 +7691,7 @@
                   <a14:compatExt spid="_x0000_s10241"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000001280000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000001280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6455,7 +7753,7 @@
                   <a14:compatExt spid="_x0000_s10242"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002280000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6517,7 +7815,7 @@
                   <a14:compatExt spid="_x0000_s10243"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003280000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6579,7 +7877,7 @@
                   <a14:compatExt spid="_x0000_s10244"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004280000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004280000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6621,7 +7919,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -6646,7 +7944,7 @@
                   <a14:compatExt spid="_x0000_s81921"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000001400100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000001400100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6708,7 +8006,7 @@
                   <a14:compatExt spid="_x0000_s81922"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002400100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002400100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6770,7 +8068,7 @@
                   <a14:compatExt spid="_x0000_s81923"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003400100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000003400100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6832,7 +8130,7 @@
                   <a14:compatExt spid="_x0000_s81925"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005400100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000005400100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6894,7 +8192,7 @@
                   <a14:compatExt spid="_x0000_s81926"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006400100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000006400100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6956,7 +8254,7 @@
                   <a14:compatExt spid="_x0000_s81927"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007400100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000007400100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6998,7 +8296,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -7023,7 +8321,7 @@
                   <a14:compatExt spid="_x0000_s4097"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000001100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000001100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7085,7 +8383,7 @@
                   <a14:compatExt spid="_x0000_s4098"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7147,7 +8445,7 @@
                   <a14:compatExt spid="_x0000_s4099"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000003100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7209,7 +8507,7 @@
                   <a14:compatExt spid="_x0000_s4100"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000004100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7271,7 +8569,7 @@
                   <a14:compatExt spid="_x0000_s4101"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000005100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000005100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7313,640 +8611,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>495300</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>133350</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>657225</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="59398" name="_ActiveXWrapper1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s59398"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000006E80000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>800100</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>66675</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="59399" name="_ActiveXWrapper2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s59399"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000007E80000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>485775</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>695325</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="59400" name="_ActiveXWrapper3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s59400"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000008E80000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>95250</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>647700</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="59401" name="_ActiveXWrapper4" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s59401"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000009E80000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>38100</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>542925</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3073" name="_ActiveXWrapper1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-0000010C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>561975</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>295275</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3074" name="_ActiveXWrapper2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3074"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-0000020C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>28575</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>123825</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>581025</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3075" name="_ActiveXWrapper7" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-0000030C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>723900</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>123825</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>457200</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3076" name="_ActiveXWrapper8" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-0000040C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>581025</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>123825</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>276225</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3077" name="_ActiveXWrapper5" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-0000050C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>714375</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>47625</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>485775</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3078" name="_ActiveXWrapper6" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-0000060C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7984,7 +8652,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -8090,7 +8758,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8232,7 +8900,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -8254,6 +8922,492 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C7D071-5CAD-4E99-8878-39A60CDC47FD}">
+  <sheetPr codeName="Planilha4"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="20.85546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" style="16" customWidth="1"/>
+    <col min="4" max="5" width="20.85546875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" style="8" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4097" r:id="rId4" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>66675</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1228725</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4097" r:id="rId4" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4098" r:id="rId6" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>38100</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1200150</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4098" r:id="rId6" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4099" r:id="rId8" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>76200</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1238250</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4099" r:id="rId8" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4100" r:id="rId10" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>38100</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1200150</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4100" r:id="rId10" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="4101" r:id="rId12" name="_ActiveXWrapper5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1381125</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1152525</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="4101" r:id="rId12" name="_ActiveXWrapper5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4530B2B6-CBE7-4A07-A94E-38245FAD7DC4}">
+  <sheetPr codeName="Planilha15"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="9" max="9" width="44.140625" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" customWidth="1"/>
+    <col min="11" max="11" width="25.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="59398" r:id="rId4" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>495300</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>657225</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="59398" r:id="rId4" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="59399" r:id="rId6" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>800100</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="59399" r:id="rId6" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="59400" r:id="rId8" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>485775</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>695325</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="59400" r:id="rId8" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="59401" r:id="rId10" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>647700</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="59401" r:id="rId10" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3398AC-EC0F-419C-B3DC-65B3AA806674}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:K9"/>
@@ -8473,7 +9627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6501534D-9E8E-453D-B261-17754C05062B}">
   <sheetPr codeName="Planilha8"/>
   <dimension ref="A1:V9"/>
@@ -8730,7 +9884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65868A2-DCF3-4B58-8FC9-A2E1AFA45DB8}">
   <sheetPr codeName="Planilha16"/>
   <dimension ref="A1:E9"/>
@@ -8926,7 +10080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BFFD6B-F025-4A6C-B5AB-3400A77FCA55}">
   <sheetPr codeName="Planilha14"/>
   <dimension ref="A1:XFC9"/>
@@ -9186,7 +10340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6887E50-4B5B-4958-BEC7-9559CB8AE07E}">
   <sheetPr codeName="Planilha9"/>
   <dimension ref="A1:V9"/>
@@ -9416,10 +10570,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF22919-66D6-4ABA-AD2C-41EBDF00D9EF}">
   <sheetPr codeName="Planilha6"/>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="8" customWidth="1"/>
@@ -9428,18 +10582,22 @@
     <col min="10" max="11" width="19.42578125" style="8" customWidth="1"/>
     <col min="12" max="12" width="33" style="8" customWidth="1"/>
     <col min="13" max="16" width="19.42578125" style="8" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" hidden="1"/>
+    <col min="17" max="17" width="11.28515625" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:20" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>23</v>
       </c>
@@ -9487,6 +10645,18 @@
       </c>
       <c r="P9" s="14" t="s">
         <v>33</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -9625,7 +10795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0072E283-C6BA-465A-B3D9-3E352E0FBDD3}">
   <sheetPr codeName="Planilha13"/>
   <dimension ref="A1:D9"/>
@@ -9836,7 +11006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3264FF35-57A0-4672-8235-169B3D48197D}">
   <sheetPr codeName="Planilha10"/>
   <dimension ref="A1:V9"/>
@@ -10060,206 +11230,6 @@
       </mc:Choice>
       <mc:Fallback>
         <control shapeId="24582" r:id="rId12" name="_ActiveXWrapper10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04BC81C-AF4F-4056-AB23-1893055E9200}">
-  <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="20.7109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" style="8" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" style="31" customWidth="1"/>
-    <col min="7" max="13" width="20.7109375" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A9:M9" xr:uid="{D04BC81C-AF4F-4056-AB23-1893055E9200}"/>
-  <dataConsolidate/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="6149" r:id="rId4" name="_ActiveXWrapper5">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1333500</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>47625</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>1114425</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="6149" r:id="rId4" name="_ActiveXWrapper5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="6148" r:id="rId6" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>1247775</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>1028700</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="6148" r:id="rId6" name="_ActiveXWrapper4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="6147" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1333500</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>1114425</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="6147" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="6146" r:id="rId10" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1171575</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="6146" r:id="rId10" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="6145" r:id="rId12" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>47625</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1152525</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="6145" r:id="rId12" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -11113,6 +12083,206 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04BC81C-AF4F-4056-AB23-1893055E9200}">
+  <sheetPr codeName="Planilha5"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="20.7109375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="16" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="8" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" style="31" customWidth="1"/>
+    <col min="7" max="13" width="20.7109375" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A9:M9" xr:uid="{D04BC81C-AF4F-4056-AB23-1893055E9200}"/>
+  <dataConsolidate/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6149" r:id="rId4" name="_ActiveXWrapper5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1333500</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>1114425</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6149" r:id="rId4" name="_ActiveXWrapper5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6148" r:id="rId6" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>1247775</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>1028700</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6148" r:id="rId6" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6147" r:id="rId8" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1333500</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>1114425</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6147" r:id="rId8" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6146" r:id="rId10" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1171575</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>114300</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6146" r:id="rId10" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6145" r:id="rId12" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1152525</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6145" r:id="rId12" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56CA9B18-EF9B-453A-AAFF-36E7CF28381C}">
   <sheetPr codeName="Planilha18"/>
@@ -11388,6 +12558,445 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8DDDB00-826E-4B54-AB4E-71DB02E32A72}">
+  <sheetPr codeName="Planilha19"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" style="8" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="27.42578125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="112646" r:id="rId4" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>838200</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>1276350</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="112646" r:id="rId4" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="112645" r:id="rId6" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1238250</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>790575</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="112645" r:id="rId6" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="112643" r:id="rId8" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1533525</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1171575</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="112643" r:id="rId8" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="112644" r:id="rId10" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1533525</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1171575</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="112644" r:id="rId10" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98FB99C-9BC1-457C-8F0A-404375E2BE9A}">
+  <sheetPr codeName="Planilha20"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="130056" r:id="rId4" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>866775</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1066800</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="130056" r:id="rId4" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="130055" r:id="rId6" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1000125</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>819150</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="130055" r:id="rId6" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="130054" r:id="rId8" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>1381125</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>933450</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="130054" r:id="rId8" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="130053" r:id="rId10" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>1381125</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>933450</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="130053" r:id="rId10" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A48F37D-DF27-4112-948E-984B6F5D08FB}">
   <sheetPr codeName="Planilha12"/>
   <dimension ref="A1:L9"/>
@@ -11672,7 +13281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7625DE08-E0FE-46F4-9267-5999D70A38A3}">
   <sheetPr codeName="Planilha11"/>
   <dimension ref="A1:J9"/>
@@ -11922,7 +13531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765C0307-1BBC-4F1B-A539-9EA2DDDB1C4B}">
   <sheetPr codeName="Planilha7"/>
   <dimension ref="A1:I9"/>
@@ -12086,7 +13695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E460CD7-AF1F-40AA-B137-8581E0E3D86F}">
   <sheetPr codeName="Planilha17"/>
   <dimension ref="A1:N9"/>
@@ -12439,490 +14048,4 @@
     </mc:AlternateContent>
   </controls>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C7D071-5CAD-4E99-8878-39A60CDC47FD}">
-  <sheetPr codeName="Planilha4"/>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="20.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="16" customWidth="1"/>
-    <col min="4" max="5" width="20.85546875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" style="8" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" style="8" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataConsolidate/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="4097" r:id="rId4" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>66675</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1228725</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="4097" r:id="rId4" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="4098" r:id="rId6" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1200150</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="4098" r:id="rId6" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="4099" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>76200</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1238250</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="4099" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="4100" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1200150</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="4100" r:id="rId10" name="_ActiveXWrapper4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="4101" r:id="rId12" name="_ActiveXWrapper5">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1381125</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1152525</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="4101" r:id="rId12" name="_ActiveXWrapper5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4530B2B6-CBE7-4A07-A94E-38245FAD7DC4}">
-  <sheetPr codeName="Planilha15"/>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17" style="8" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" customWidth="1"/>
-    <col min="9" max="9" width="44.140625" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" customWidth="1"/>
-    <col min="11" max="11" width="25.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="22.7109375" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="17"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataConsolidate/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="59398" r:id="rId4" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>495300</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>657225</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="59398" r:id="rId4" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="59399" r:id="rId6" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>800100</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="59399" r:id="rId6" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="59400" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>485775</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>695325</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="59400" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="59401" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>95250</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>647700</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>47625</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="59401" r:id="rId10" name="_ActiveXWrapper4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
-</worksheet>
 </file>
--- a/DotNetExcel/StarkBankExcel/StarkBank.xlsx
+++ b/DotNetExcel/StarkBankExcel/StarkBank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stark - Admin\Documents\deploy-cartshop-hoje\sdk-excel\DotNetExcel\StarkBankExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BA3AFE-86C2-46EE-8E48-024DBB5595E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD92FA38-380F-491F-9E3C-14E68F43393D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="15375" windowHeight="7785" firstSheet="1" activeTab="1" xr2:uid="{DD233689-9B57-48BF-9576-9FA43391D3F3}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7785" firstSheet="1" activeTab="2" xr2:uid="{DD233689-9B57-48BF-9576-9FA43391D3F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="2" state="hidden" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="123">
   <si>
     <t>Chave Pix</t>
   </si>
@@ -430,6 +430,9 @@
   <si>
     <t>Stark Bank SDK Excel - v3.1.7</t>
   </si>
+  <si>
+    <t>Nome do CardHolder</t>
+  </si>
 </sst>
 </file>
 
@@ -714,6 +717,125 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="23A4525A1295E524FB7284BA2EA2DC8317EF42"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="17053D61D1F15A1482019B2C1A4E6D57E3A971"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX100.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="423CD9C0343555445FB48C9D4CF7D65D1F3284"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX101.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="560AC6FB15F17754F6558A0F58035E0AF7ED85"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="19A5453E610F18142DA1BAA91D29A587ED2E11"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4313"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1D58F8DCE161321493A19D8C10118F3363B411"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="10F831FB013D30140151820D1AB0BB140FD961"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX14.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
   <ax:ocxPr ax:name="Cookie" ax:value="28A34ED1D2633F2429D291182761C070389522"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
@@ -726,92 +848,92 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX15.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1626B229C1652514446181B314A00A77AF6681"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="15BA0FB321DE6D148D81BF60113447A8E50371"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1376"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX100.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX16.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2596667A2285C4241122B3CF25CD7B218043C2"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2AE3450482C58E244C5291B3282A90F9A78E42"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX101.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX17.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1F6AA8BD81815014DA61A5D71870FA81614161"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="397AE3E0A32833341B5399FC391E12926F72C3"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3175"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1482"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX18.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1F70BF05619C7F14D001A2031EA2288CEEF621"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5974E136658C5454320585C85BAB48B9439E65"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX19.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="23FDAD7A329F60245422A56B22EA1482F84402"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5C7587ECD589D954AF5588B7511831DB11F6C5"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -828,131 +950,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX14.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="23A4525A1295E524FB7284BA2EA2DC8317EF42"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX15.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5974E136658C5454320585C85BAB48B9439E65"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX16.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="397AE3E0A32833341B5399FC391E12926F72C3"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX17.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2AE3450482C58E244C5291B3282A90F9A78E42"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX18.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="15BA0FB321DE6D148D81BF60113447A8E50371"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX19.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="128C09B0A1B301143F11A201102466FA8162A1"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="10F831FB013D30140151820D1AB0BB140FD961"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
 <file path=xl/activeX/activeX20.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2E7AFE3552B17824A73291B82F5C62F7F66CC2"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4BC486F6B4C83A44D6048B974C96446332A854"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -986,7 +989,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4BC486F6B4C83A44D6048B974C96446332A854"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2E7AFE3552B17824A73291B82F5C62F7F66CC2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1003,7 +1006,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5C7587ECD589D954AF5588B7511831DB11F6C5"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="128C09B0A1B301143F11A201102466FA8162A1"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1016,6 +1019,57 @@
 </file>
 
 <file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5664E4FA354E53547A85877C5681815C86E255"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3E72B73533463334A09396C63850D5D3146F23"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="276984BE82622724D2829AD32CC77B450D8CB2"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1032,87 +1086,36 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="276984BE82622724D2829AD32CC77B450D8CB2"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="80815DC5B82C3B8498489E26894C5C52875E28"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3757"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1588"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3E72B73533463334A09396C63850D5D3146F23"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="71F4FF3617034374D487A4537B51302A0C89B7"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5664E4FA354E53547A85877C5681815C86E255"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3466"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="43935BDA7439194471449D234CFD527D9886B4"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5FE4E9EDE5117D54C395AB0B52D849B4179075"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -1122,7 +1125,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1D58F8DCE161321493A19D8C10118F3363B411"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="23FDAD7A329F60245422A56B22EA1482F84402"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1156,14 +1159,14 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="71F4FF3617034374D487A4537B51302A0C89B7"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5FE4E9EDE5117D54C395AB0B52D849B4179075"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -1173,19 +1176,70 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="80815DC5B82C3B8498489E26894C5C52875E28"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="43935BDA7439194471449D234CFD527D9886B4"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3757"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1588"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
 <file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="6D72D142762FA7648186B99160B384DA4EEAD6"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="576D85FB2525B8547055A14351ED593B73E215"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3201"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX35.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4DD8155564BBBB442F449A794155F293DF1F94"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX36.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1202,12 +1256,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX37.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4DD8155564BBBB442F449A794155F293DF1F94"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4BDD5BFBC494C944E75484BA43B9AFC575EDE4"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1219,29 +1273,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX38.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="576D85FB2525B8547055A14351ED593B73E215"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3201"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX36.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="6D72D142762FA7648186B99160B384DA4EEAD6"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="36BF4D76D36CAA346A9392633D35C8E7F4F293"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1253,7 +1290,41 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX39.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="21156A5D42671D24110290D22610E26CEF0122"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1F70BF05619C7F14D001A2031EA2288CEEF621"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX40.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1270,75 +1341,92 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX41.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="21156A5D42671D24110290D22610E26CEF0122"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="7C9BBDE4E751B574F557BC077FC280926F0487"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX42.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="36BF4D76D36CAA346A9392633D35C8E7F4F293"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="6EAFFE9C06D4276431A6BB2F6072D3CF2C1786"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX43.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="19A5453E610F18142DA1BAA91D29A587ED2E11"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1BF3F766D1EC8E14D641AB8818D8695A960D41"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4313"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX44.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4BDD5BFBC494C944E75484BA43B9AFC575EDE4"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="29E4B6D5F2B5EF24B732AC612476A095FC12F2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX45.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3AA2985733B4083434D3B3DA395B83B5AB5FB3"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX46.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1355,97 +1443,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX42.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3AA2985733B4083434D3B3DA395B83B5AB5FB3"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX43.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="29E4B6D5F2B5EF24B732AC612476A095FC12F2"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX44.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1BF3F766D1EC8E14D641AB8818D8695A960D41"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX45.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="6EAFFE9C06D4276431A6BB2F6072D3CF2C1786"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX46.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="7C9BBDE4E751B574F557BC077FC280926F0487"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3678"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1640"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
 <file path=xl/activeX/activeX47.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1D3C8440119274147F5190E81CB29314F1A0B1"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5F3C3A5AA5DBB654AFD5A7C25896612CBE6DC5"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1462,7 +1465,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2F27997732C2CB2441C298BB24A21C18565F42"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4725C0A2E4AB894430D4AEF74EE21D1AD6A734"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1496,14 +1499,14 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="17053D61D1F15A1482019B2C1A4E6D57E3A971"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1626B229C1652514446181B314A00A77AF6681"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1376"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -1513,7 +1516,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4725C0A2E4AB894430D4AEF74EE21D1AD6A734"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2F27997732C2CB2441C298BB24A21C18565F42"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1530,7 +1533,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5F3C3A5AA5DBB654AFD5A7C25896612CBE6DC5"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1D3C8440119274147F5190E81CB29314F1A0B1"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1543,6 +1546,57 @@
 </file>
 
 <file path=xl/activeX/activeX52.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="9C5D0F81D9A7DC9451D986E29349E294E0E0F9"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX53.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="8A681C04683975842508B2258073BEA1C60FD8"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX54.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="7B414461476FE874FCC7AF487111D4DE5C31F7"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX55.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1559,58 +1613,109 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX56.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="7B414461476FE874FCC7AF487111D4DE5C31F7"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="190EB7A1C18BFD142EB1A75D1D8ECE9AC6A921"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3096"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1244"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX57.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="8A681C04683975842508B2258073BEA1C60FD8"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2F31A0EA52B80A243F02887A226A80BA2346A2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3334"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1217"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX58.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="9C5D0F81D9A7DC9451D986E29349E294E0E0F9"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3443F6D933A917348513994830A35447867593"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX59.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4EDC5AE2D4725F442D54BDB348E5FBB86B52C4"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1DB344D2F14249140061BD5D11E614111405C1"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4392"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1376"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX60.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="581AFF66D5395E54CBC5BEBA52A895EF8D96F5"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX61.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1627,12 +1732,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX62.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="581AFF66D5395E54CBC5BEBA52A895EF8D96F5"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="64B7B760262CDD643836A79A641DDB36424F16"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1644,12 +1749,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX63.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4EDC5AE2D4725F442D54BDB348E5FBB86B52C4"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="192AED9321906F1430518AA91C61F691A49AE1"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1661,12 +1766,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX64.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3443F6D933A917348513994830A35447867593"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2FAFF23AA2246924D782B58F21CB01DE2B8C82"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1678,58 +1783,41 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX65.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1D1500907189BD14DA51B2181B162FBD75FE31"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="393B0D4DB376B1348C53AA283ED005A8E39383"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1376"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX66.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2F31A0EA52B80A243F02887A226A80BA2346A2"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="43443F65340DC5448034B84249A78BF6899C14"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3334"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1217"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX61.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="190EB7A1C18BFD142EB1A75D1D8ECE9AC6A921"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3096"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1244"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX67.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1746,92 +1834,75 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX68.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="43443F65340DC5448034B84249A78BF6899C14"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="41CF79F694E72D449634A36244C31DA4F7C064"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX69.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="393B0D4DB376B1348C53AA283ED005A8E39383"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="340115F7C331F8342C23902032B2E1FE922923"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="2FAFF23AA2246924D782B58F21CB01DE2B8C82"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1CC3318201EE2A1421C19CEB15987574AED511"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX70.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="192AED9321906F1430518AA91C61F691A49AE1"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="209AD430929B0C246352BB46205966BBA32BE2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX67.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="64B7B760262CDD643836A79A641DDB36424F16"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX71.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
@@ -1848,80 +1919,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX69.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="209AD430929B0C246352BB46205966BBA32BE2"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3836"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1773"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1BD6BA4211BC3E14DAF185961A2B376D133421"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1376"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX70.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="340115F7C331F8342C23902032B2E1FE922923"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3810"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1799"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX71.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="41CF79F694E72D449634A36244C31DA4F7C064"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3969"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1720"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
 <file path=xl/activeX/activeX72.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1FF48C76A17A8C14A1D1B461189CB6BA129791"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5FCC13B9257A75548E65A9E458AA0E6A413BF5"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1938,7 +1941,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="23587ECD629DA1245032AC232F0D6B45106E92"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4F2081B3648833443864BB8143FD2C02F9E634"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1972,7 +1975,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4F2081B3648833443864BB8143FD2C02F9E634"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="23587ECD629DA1245032AC232F0D6B45106E92"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -1989,7 +1992,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5FCC13B9257A75548E65A9E458AA0E6A413BF5"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1FF48C76A17A8C14A1D1B461189CB6BA129791"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2006,7 +2009,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5B4A34D975B853543985A7E75523690B60EC35"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="19726D3BD1AD01142191B2C41B5B2D13E650B1"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2023,7 +2026,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="42576A9D548EA54490F4BA2045852D9EEA0264"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="207D2713820AB8246622A7CD26A57A9DCA2162"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2057,14 +2060,14 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1CC3318201EE2A1421C19CEB15987574AED511"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1BD6BA4211BC3E14DAF185961A2B376D133421"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1455"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1376"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -2074,7 +2077,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="207D2713820AB8246622A7CD26A57A9DCA2162"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="42576A9D548EA54490F4BA2045852D9EEA0264"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2091,7 +2094,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="19726D3BD1AD01142191B2C41B5B2D13E650B1"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5B4A34D975B853543985A7E75523690B60EC35"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2108,14 +2111,14 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1B7A977A61ADF41453E1BBBE1183429619DB11"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="51A95A66553942547D759A7153A00908FCA885"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3281"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -2125,7 +2128,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="232EEE2C927B21244D728DA228DC1AAB22C9E2"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="4E23FE0EC4C93C4470948DA849AEEC73F9C744"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2159,7 +2162,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="4E23FE0EC4C93C4470948DA849AEEC73F9C744"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="232EEE2C927B21244D728DA228DC1AAB22C9E2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2176,7 +2179,24 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="51A95A66553942547D759A7153A00908FCA885"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1B7A977A61ADF41453E1BBBE1183429619DB11"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3281"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX87.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="632A921A961CC6648D5697386AA1DF460A0236"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2188,35 +2208,18 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX88.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="5B4126E875ABC55427F5B28E55218522354BA5"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="245B62680258F8244B928BF02F0D73C394B3A2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
   <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
-<file path=xl/activeX/activeX88.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="43953CE6E45013447B8491244183EC3B869614"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3149"/>
   <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
@@ -2244,13 +2247,13 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1DB344D2F14249140061BD5D11E614111405C1"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1D1500907189BD14DA51B2181B162FBD75FE31"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="4392"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="4419"/>
   <ax:ocxPr ax:name="Sizel_cy" ax:value="1376"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
@@ -2261,7 +2264,24 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="245B62680258F8244B928BF02F0D73C394B3A2"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="43953CE6E45013447B8491244183EC3B869614"/>
+  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
+  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
+  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3149"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
+  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
+</ax:ocx>
+</file>
+
+<file path=xl/activeX/activeX91.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
+  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
+  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
+  <ax:ocxPr ax:name="Cookie" ax:value="5B4126E875ABC55427F5B28E55218522354BA5"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2273,12 +2293,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/activeX/activeX92.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="632A921A961CC6648D5697386AA1DF460A0236"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="676BBF00A6812B64BBB6BA716DB953807A8EA6"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2290,29 +2310,12 @@
 </ax:ocx>
 </file>
 
-<file path=xl/activeX/activeX92.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
-  <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
-  <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="482B56B2D4F09144EA9495AD4E1391B3ADA544"/>
-  <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
-  <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
-  <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1535"/>
-  <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
-</ax:ocx>
-</file>
-
 <file path=xl/activeX/activeX93.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{A37BBB42-E8C1-4E09-B9CA-F009CE620C08}" ax:persistence="persistPropertyBag">
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="3C148BBC83328034CB4383F53575DFC2E2D673"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1441CBD291E7921466418469122C7CFF2CD931"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2346,7 +2349,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="1441CBD291E7921466418469122C7CFF2CD931"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="3C148BBC83328034CB4383F53575DFC2E2D673"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2363,7 +2366,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="676BBF00A6812B64BBB6BA716DB953807A8EA6"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="482B56B2D4F09144EA9495AD4E1391B3ADA544"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -2380,14 +2383,14 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="560AC6FB15F17754F6558A0F58035E0AF7ED85"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="1F6AA8BD81815014DA61A5D71870FA81614161"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_dwFlags" ax:value="0"/>
   <ax:ocxPr ax:name="MiscStatusBits" ax:value="0"/>
-  <ax:ocxPr ax:name="Sizel_cx" ax:value="3228"/>
-  <ax:ocxPr ax:name="Sizel_cy" ax:value="1429"/>
+  <ax:ocxPr ax:name="Sizel_cx" ax:value="3175"/>
+  <ax:ocxPr ax:name="Sizel_cy" ax:value="1482"/>
   <ax:ocxPr ax:name="IsDynamic" ax:value="0"/>
 </ax:ocx>
 </file>
@@ -2397,7 +2400,7 @@
   <ax:ocxPr ax:name="RawObjectTypeName" ax:value="System.Windows.Forms.Button"/>
   <ax:ocxPr ax:name="RawObjectAssemblyName" ax:value="System.Windows.Forms, Version=4.0.0.0, Culture=neutral, PublicKeyToken=b77a5c561934e089"/>
   <ax:ocxPr ax:name="RawObjectAssemblyPath" ax:value=""/>
-  <ax:ocxPr ax:name="Cookie" ax:value="423CD9C0343555445FB48C9D4CF7D65D1F3284"/>
+  <ax:ocxPr ax:name="Cookie" ax:value="2596667A2285C4241122B3CF25CD7B218043C2"/>
   <ax:ocxPr ax:name="ControlInfo_cb" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_hAccel" ax:value="0"/>
   <ax:ocxPr ax:name="ControlInfo_cAccel" ax:value="0"/>
@@ -6455,13 +6458,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>3</xdr:col>
+          <xdr:col>4</xdr:col>
           <xdr:colOff>523875</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>28575</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
+          <xdr:col>5</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
           <xdr:row>7</xdr:row>
           <xdr:rowOff>47625</xdr:rowOff>
@@ -6475,6 +6478,68 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001740100}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>419100</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>85725</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>476250</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>152400</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="95234" name="_ActiveXWrapper2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s95234"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002740100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6518,25 +6583,25 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>419100</xdr:colOff>
+          <xdr:colOff>504825</xdr:colOff>
           <xdr:row>0</xdr:row>
           <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>314325</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
+          <xdr:rowOff>161925</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="95234" name="_ActiveXWrapper2" hidden="1">
+            <xdr:cNvPr id="95235" name="_ActiveXWrapper3" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s95234"/>
+                  <a14:compatExt spid="_x0000_s95235"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002740100}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003740100}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -6579,75 +6644,13 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>504825</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>85725</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>314325</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>161925</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="95235" name="_ActiveXWrapper3" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s95235"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003740100}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>581025</xdr:colOff>
           <xdr:row>0</xdr:row>
           <xdr:rowOff>114300</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>6</xdr:col>
+          <xdr:col>7</xdr:col>
           <xdr:colOff>752475</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>161925</xdr:rowOff>
@@ -9163,52 +9166,52 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="4097" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="4101" r:id="rId4" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>66675</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1381125</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1228725</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1152525</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="4097" r:id="rId4" name="_ActiveXWrapper1"/>
+        <control shapeId="4101" r:id="rId4" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="4098" r:id="rId6" name="_ActiveXWrapper2">
+        <control shapeId="4100" r:id="rId6" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1200150</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="4098" r:id="rId6" name="_ActiveXWrapper2"/>
+        <control shapeId="4100" r:id="rId6" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -9238,52 +9241,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="4100" r:id="rId10" name="_ActiveXWrapper4">
+        <control shapeId="4098" r:id="rId10" name="_ActiveXWrapper2">
           <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>1200150</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="4100" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="4098" r:id="rId10" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="4101" r:id="rId12" name="_ActiveXWrapper5">
+        <control shapeId="4097" r:id="rId12" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1381125</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>66675</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1152525</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1228725</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="4101" r:id="rId12" name="_ActiveXWrapper5"/>
+        <control shapeId="4097" r:id="rId12" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -9482,8 +9485,83 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="59398" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="59401" r:id="rId4" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>95250</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>647700</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="59401" r:id="rId4" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="59400" r:id="rId6" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>485775</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>695325</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="59400" r:id="rId6" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="59399" r:id="rId8" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>800100</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="59399" r:id="rId8" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="59398" r:id="rId10" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
@@ -9502,82 +9580,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="59398" r:id="rId4" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="59399" r:id="rId6" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>800100</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="59399" r:id="rId6" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="59400" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>485775</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>695325</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="59400" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="59401" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>95250</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>647700</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>47625</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="59401" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="59398" r:id="rId10" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -9652,8 +9655,133 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3078" r:id="rId4" name="_ActiveXWrapper6">
+        <control shapeId="3073" r:id="rId4" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>38100</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>542925</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3073" r:id="rId4" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3074" r:id="rId6" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>561975</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>295275</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3074" r:id="rId6" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3075" r:id="rId8" name="_ActiveXWrapper7">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>28575</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>581025</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3075" r:id="rId8" name="_ActiveXWrapper7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3076" r:id="rId10" name="_ActiveXWrapper8">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>723900</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>457200</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3076" r:id="rId10" name="_ActiveXWrapper8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3077" r:id="rId12" name="_ActiveXWrapper5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>581025</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>276225</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="3077" r:id="rId12" name="_ActiveXWrapper5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="3078" r:id="rId14" name="_ActiveXWrapper6">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>3</xdr:col>
@@ -9672,132 +9800,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3078" r:id="rId4" name="_ActiveXWrapper6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3077" r:id="rId6" name="_ActiveXWrapper5">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>581025</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>276225</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3077" r:id="rId6" name="_ActiveXWrapper5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3076" r:id="rId8" name="_ActiveXWrapper8">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>723900</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>457200</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3076" r:id="rId8" name="_ActiveXWrapper8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3075" r:id="rId10" name="_ActiveXWrapper7">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>28575</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>581025</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3075" r:id="rId10" name="_ActiveXWrapper7"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3074" r:id="rId12" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>561975</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>47625</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>295275</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3074" r:id="rId12" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3073" r:id="rId14" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>542925</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3073" r:id="rId14" name="_ActiveXWrapper1"/>
+        <control shapeId="3078" r:id="rId14" name="_ActiveXWrapper6"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -9909,8 +9912,133 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="16389" r:id="rId4" name="_ActiveXWrapper5">
+        <control shapeId="16390" r:id="rId4" name="_ActiveXWrapper6">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1209675</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>981075</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="16390" r:id="rId4" name="_ActiveXWrapper6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="16385" r:id="rId6" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1162050</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="16385" r:id="rId6" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="16386" r:id="rId8" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1162050</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="16386" r:id="rId8" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="16387" r:id="rId10" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1304925</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1076325</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="16387" r:id="rId10" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="16388" r:id="rId12" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1200150</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="16388" r:id="rId12" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="16389" r:id="rId14" name="_ActiveXWrapper5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>3</xdr:col>
@@ -9929,132 +10057,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="16389" r:id="rId4" name="_ActiveXWrapper5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="16388" r:id="rId6" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1200150</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>971550</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="16388" r:id="rId6" name="_ActiveXWrapper4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="16387" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1304925</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1076325</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="16387" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="16386" r:id="rId10" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1162050</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="16386" r:id="rId10" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="16385" r:id="rId12" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1162050</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="16385" r:id="rId12" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="16390" r:id="rId14" name="_ActiveXWrapper6">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1209675</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>981075</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="16390" r:id="rId14" name="_ActiveXWrapper6"/>
+        <control shapeId="16389" r:id="rId14" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -10155,8 +10158,83 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="73729" r:id="rId3" name="_ActiveXWrapper1">
+        <control shapeId="73732" r:id="rId3" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>552450</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>419100</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>142875</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="73732" r:id="rId3" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="73731" r:id="rId5" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId6">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>1304925</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>533400</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="73731" r:id="rId5" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="73730" r:id="rId7" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId8">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>638175</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>466725</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="73730" r:id="rId7" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="73729" r:id="rId9" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId10">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
@@ -10175,82 +10253,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="73729" r:id="rId3" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="73730" r:id="rId5" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId6">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>638175</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>466725</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="73730" r:id="rId5" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="73731" r:id="rId7" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>1304925</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>533400</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="73731" r:id="rId7" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="73732" r:id="rId9" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId10">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>552450</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>419100</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="73732" r:id="rId9" name="_ActiveXWrapper4"/>
+        <control shapeId="73729" r:id="rId9" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -10390,52 +10393,52 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="52225" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="52229" r:id="rId4" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
+                <xdr:colOff>1266825</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
+                <xdr:rowOff>171450</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>1181100</xdr:colOff>
+                <xdr:colOff>2428875</xdr:colOff>
                 <xdr:row>6</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
+                <xdr:rowOff>152400</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="52225" r:id="rId4" name="_ActiveXWrapper1"/>
+        <control shapeId="52229" r:id="rId4" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="52226" r:id="rId6" name="_ActiveXWrapper2">
+        <control shapeId="52228" r:id="rId6" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
+                <xdr:colOff>2514600</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
+                <xdr:rowOff>104775</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1171575</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>723900</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="52226" r:id="rId6" name="_ActiveXWrapper2"/>
+        <control shapeId="52228" r:id="rId6" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10465,52 +10468,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="52228" r:id="rId10" name="_ActiveXWrapper4">
+        <control shapeId="52226" r:id="rId10" name="_ActiveXWrapper2">
           <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>2514600</xdr:colOff>
+                <xdr:colOff>9525</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
+                <xdr:rowOff>95250</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>723900</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1171575</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="52228" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="52226" r:id="rId10" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="52229" r:id="rId12" name="_ActiveXWrapper5">
+        <control shapeId="52225" r:id="rId12" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>1266825</xdr:colOff>
+                <xdr:colOff>19050</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
+                <xdr:rowOff>180975</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>2428875</xdr:colOff>
+                <xdr:colOff>1181100</xdr:colOff>
                 <xdr:row>6</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
+                <xdr:rowOff>161925</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="52229" r:id="rId12" name="_ActiveXWrapper5"/>
+        <control shapeId="52225" r:id="rId12" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -10620,52 +10623,52 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="20485" r:id="rId4" name="_ActiveXWrapper5">
+        <control shapeId="20481" r:id="rId4" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>238125</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>66675</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:rowOff>57150</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>257175</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>85725</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>38100</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="20485" r:id="rId4" name="_ActiveXWrapper5"/>
+        <control shapeId="20481" r:id="rId4" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="20484" r:id="rId6" name="_ActiveXWrapper4">
+        <control shapeId="20482" r:id="rId6" name="_ActiveXWrapper2">
           <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>390525</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>57150</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
+                <xdr:rowOff>161925</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>219075</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>76200</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
+                <xdr:rowOff>142875</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="20484" r:id="rId6" name="_ActiveXWrapper4"/>
+        <control shapeId="20482" r:id="rId6" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10695,52 +10698,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="20482" r:id="rId10" name="_ActiveXWrapper2">
+        <control shapeId="20484" r:id="rId10" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>57150</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>390525</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
+                <xdr:rowOff>171450</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>76200</xdr:colOff>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>219075</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
+                <xdr:rowOff>152400</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="20482" r:id="rId10" name="_ActiveXWrapper2"/>
+        <control shapeId="20484" r:id="rId10" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="20481" r:id="rId12" name="_ActiveXWrapper1">
+        <control shapeId="20485" r:id="rId12" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>66675</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>238125</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>85725</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
+                <xdr:rowOff>57150</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="20481" r:id="rId12" name="_ActiveXWrapper1"/>
+        <control shapeId="20485" r:id="rId12" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -10844,52 +10847,52 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="8193" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="8197" r:id="rId4" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>76200</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>114300</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:rowOff>57150</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1257300</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1276350</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
+                <xdr:rowOff>38100</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="8193" r:id="rId4" name="_ActiveXWrapper1"/>
+        <control shapeId="8197" r:id="rId4" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="8194" r:id="rId6" name="_ActiveXWrapper2">
+        <control shapeId="8196" r:id="rId6" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>85725</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>114300</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
+                <xdr:rowOff>171450</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1247775</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1276350</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
+                <xdr:rowOff>152400</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="8194" r:id="rId6" name="_ActiveXWrapper2"/>
+        <control shapeId="8196" r:id="rId6" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10919,52 +10922,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="8196" r:id="rId10" name="_ActiveXWrapper4">
+        <control shapeId="8194" r:id="rId10" name="_ActiveXWrapper2">
           <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>114300</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>85725</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
+                <xdr:rowOff>161925</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1276350</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1247775</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
+                <xdr:rowOff>142875</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="8196" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="8194" r:id="rId10" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="8197" r:id="rId12" name="_ActiveXWrapper5">
+        <control shapeId="8193" r:id="rId12" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>114300</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>76200</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1276350</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1257300</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
+                <xdr:rowOff>19050</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="8197" r:id="rId12" name="_ActiveXWrapper5"/>
+        <control shapeId="8193" r:id="rId12" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -11055,18 +11058,18 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="49157" r:id="rId4" name="_ActiveXWrapper5">
+        <control shapeId="49158" r:id="rId4" name="_ActiveXWrapper10">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>1485900</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>876300</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>171450</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>685800</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>828675</xdr:colOff>
                 <xdr:row>6</xdr:row>
                 <xdr:rowOff>152400</xdr:rowOff>
               </to>
@@ -11075,32 +11078,32 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="49157" r:id="rId4" name="_ActiveXWrapper5"/>
+        <control shapeId="49158" r:id="rId4" name="_ActiveXWrapper10"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="49156" r:id="rId6" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId7">
+        <control shapeId="49154" r:id="rId6" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>942975</xdr:colOff>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>1495425</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
+                <xdr:rowOff>104775</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>2076450</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>695325</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="49156" r:id="rId6" name="_ActiveXWrapper4"/>
+        <control shapeId="49154" r:id="rId6" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -11130,43 +11133,43 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="49154" r:id="rId10" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+        <control shapeId="49156" r:id="rId10" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>1495425</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>942975</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
+                <xdr:rowOff>114300</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>695325</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>2076450</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
+                <xdr:rowOff>95250</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="49154" r:id="rId10" name="_ActiveXWrapper2"/>
+        <control shapeId="49156" r:id="rId10" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="49158" r:id="rId12" name="_ActiveXWrapper10">
+        <control shapeId="49157" r:id="rId12" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>876300</xdr:colOff>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>1485900</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>171450</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>828675</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>685800</xdr:colOff>
                 <xdr:row>6</xdr:row>
                 <xdr:rowOff>152400</xdr:rowOff>
               </to>
@@ -11175,7 +11178,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="49158" r:id="rId12" name="_ActiveXWrapper10"/>
+        <control shapeId="49157" r:id="rId12" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -11285,52 +11288,52 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24580" r:id="rId4" name="_ActiveXWrapper4">
+        <control shapeId="24582" r:id="rId4" name="_ActiveXWrapper10">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1123950</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>1209675</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>895350</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>981075</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="24580" r:id="rId4" name="_ActiveXWrapper4"/>
+        <control shapeId="24582" r:id="rId4" name="_ActiveXWrapper10"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24579" r:id="rId6" name="_ActiveXWrapper3">
+        <control shapeId="24577" r:id="rId6" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1219200</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>1276350</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>990600</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>1047750</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="24579" r:id="rId6" name="_ActiveXWrapper3"/>
+        <control shapeId="24577" r:id="rId6" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -11360,52 +11363,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24577" r:id="rId10" name="_ActiveXWrapper1">
+        <control shapeId="24579" r:id="rId10" name="_ActiveXWrapper3">
           <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>1276350</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>1219200</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1047750</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>990600</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="24577" r:id="rId10" name="_ActiveXWrapper1"/>
+        <control shapeId="24579" r:id="rId10" name="_ActiveXWrapper3"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24582" r:id="rId12" name="_ActiveXWrapper10">
+        <control shapeId="24580" r:id="rId12" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1209675</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1123950</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>981075</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>895350</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="24582" r:id="rId12" name="_ActiveXWrapper10"/>
+        <control shapeId="24580" r:id="rId12" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -11932,8 +11935,333 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1044" r:id="rId4" name="_ActiveXWrapper11">
+        <control shapeId="1047" r:id="rId4" name="_ActiveXWrapper14">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>533400</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>19050</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>19</xdr:col>
+                <xdr:colOff>295275</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1047" r:id="rId4" name="_ActiveXWrapper14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1046" r:id="rId6" name="_ActiveXWrapper13">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>533400</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>19</xdr:col>
+                <xdr:colOff>295275</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1046" r:id="rId6" name="_ActiveXWrapper13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1045" r:id="rId8" name="_ActiveXWrapper12">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>14</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>16</xdr:col>
+                <xdr:colOff>371475</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1045" r:id="rId8" name="_ActiveXWrapper12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1041" r:id="rId10" name="_ActiveXWrapper8">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>276225</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>38100</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1041" r:id="rId10" name="_ActiveXWrapper8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1040" r:id="rId12" name="_ActiveXWrapper7">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>19050</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1040" r:id="rId12" name="_ActiveXWrapper7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1039" r:id="rId14" name="_ActiveXWrapper6">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>295275</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>47625</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1039" r:id="rId14" name="_ActiveXWrapper6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1038" r:id="rId16" name="_ActiveXWrapper5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId17">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>295275</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>57150</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1038" r:id="rId16" name="_ActiveXWrapper5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1037" r:id="rId18" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId19">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>180975</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>552450</xdr:colOff>
+                <xdr:row>1048575</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1037" r:id="rId18" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1036" r:id="rId20" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId21">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>266700</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>28575</xdr:colOff>
+                <xdr:row>1048575</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1036" r:id="rId20" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1035" r:id="rId22" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId23">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>161925</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>533400</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1035" r:id="rId22" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1025" r:id="rId24" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId25">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>247650</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>581025</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1025" r:id="rId24" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1042" r:id="rId26" name="_ActiveXWrapper9">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId27">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>295275</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>19050</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>57150</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1042" r:id="rId26" name="_ActiveXWrapper9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1043" r:id="rId28" name="_ActiveXWrapper10">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId29">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>247650</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1043" r:id="rId28" name="_ActiveXWrapper10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1044" r:id="rId30" name="_ActiveXWrapper11">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId31">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>3</xdr:col>
@@ -11952,332 +12280,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1044" r:id="rId4" name="_ActiveXWrapper11"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1043" r:id="rId6" name="_ActiveXWrapper10">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>247650</xdr:colOff>
-                <xdr:row>14</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1043" r:id="rId6" name="_ActiveXWrapper10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1042" r:id="rId8" name="_ActiveXWrapper9">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>295275</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>57150</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1042" r:id="rId8" name="_ActiveXWrapper9"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1025" r:id="rId10" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>247650</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>581025</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1025" r:id="rId10" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1035" r:id="rId12" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>161925</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>533400</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1035" r:id="rId12" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1036" r:id="rId14" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>266700</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>28575</xdr:colOff>
-                <xdr:row>1048575</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1036" r:id="rId14" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1037" r:id="rId16" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId17">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>180975</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>552450</xdr:colOff>
-                <xdr:row>1048575</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1037" r:id="rId16" name="_ActiveXWrapper4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1038" r:id="rId18" name="_ActiveXWrapper5">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId19">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>295275</xdr:colOff>
-                <xdr:row>14</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>57150</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1038" r:id="rId18" name="_ActiveXWrapper5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1039" r:id="rId20" name="_ActiveXWrapper6">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId21">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>295275</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>47625</xdr:colOff>
-                <xdr:row>20</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1039" r:id="rId20" name="_ActiveXWrapper6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1040" r:id="rId22" name="_ActiveXWrapper7">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId23">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>257175</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>13</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
-                <xdr:row>20</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1040" r:id="rId22" name="_ActiveXWrapper7"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1041" r:id="rId24" name="_ActiveXWrapper8">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId25">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>276225</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1041" r:id="rId24" name="_ActiveXWrapper8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1045" r:id="rId26" name="_ActiveXWrapper12">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId27">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>14</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>371475</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1045" r:id="rId26" name="_ActiveXWrapper12"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1046" r:id="rId28" name="_ActiveXWrapper13">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId29">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>533400</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>19</xdr:col>
-                <xdr:colOff>295275</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>171450</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1046" r:id="rId28" name="_ActiveXWrapper13"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1047" r:id="rId30" name="_ActiveXWrapper14">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId31">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>533400</xdr:colOff>
-                <xdr:row>14</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>19</xdr:col>
-                <xdr:colOff>295275</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1047" r:id="rId30" name="_ActiveXWrapper14"/>
+        <control shapeId="1044" r:id="rId30" name="_ActiveXWrapper11"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -12357,52 +12360,52 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="6149" r:id="rId4" name="_ActiveXWrapper5">
+        <control shapeId="6145" r:id="rId4" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>1333500</xdr:colOff>
+                <xdr:colOff>9525</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>47625</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>1114425</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1152525</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="6149" r:id="rId4" name="_ActiveXWrapper5"/>
+        <control shapeId="6145" r:id="rId4" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="6148" r:id="rId6" name="_ActiveXWrapper4">
+        <control shapeId="6146" r:id="rId6" name="_ActiveXWrapper2">
           <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>1247775</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
+                <xdr:rowOff>133350</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>1028700</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1171575</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
+                <xdr:rowOff>114300</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="6148" r:id="rId6" name="_ActiveXWrapper4"/>
+        <control shapeId="6146" r:id="rId6" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -12432,52 +12435,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="6146" r:id="rId10" name="_ActiveXWrapper2">
+        <control shapeId="6148" r:id="rId10" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>1247775</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
+                <xdr:rowOff>142875</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1171575</xdr:colOff>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>1028700</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
+                <xdr:rowOff>123825</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="6146" r:id="rId10" name="_ActiveXWrapper2"/>
+        <control shapeId="6148" r:id="rId10" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="6145" r:id="rId12" name="_ActiveXWrapper1">
+        <control shapeId="6149" r:id="rId12" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
+                <xdr:colOff>1333500</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>47625</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1152525</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>1114425</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="6145" r:id="rId12" name="_ActiveXWrapper1"/>
+        <control shapeId="6149" r:id="rId12" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -12487,23 +12490,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69372841-2205-4369-ABDD-15A1D3D36AA6}">
   <sheetPr codeName="Planilha18"/>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" style="8" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="24" style="8" customWidth="1"/>
-    <col min="4" max="4" width="23.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="8" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" style="8" customWidth="1"/>
-    <col min="10" max="10" width="20.85546875" style="8" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" hidden="1"/>
+    <col min="2" max="3" width="20.7109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="24" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="8" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="17"/>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -12514,8 +12517,9 @@
       <c r="H1" s="17"/>
       <c r="I1" s="17"/>
       <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -12526,8 +12530,9 @@
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -12538,8 +12543,9 @@
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -12550,8 +12556,9 @@
       <c r="H4" s="17"/>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -12562,8 +12569,9 @@
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -12574,8 +12582,9 @@
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -12586,8 +12595,9 @@
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -12598,8 +12608,9 @@
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>103</v>
       </c>
@@ -12607,38 +12618,42 @@
         <v>104</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="E9" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="I9" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="J9" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="K9" s="13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="C10" s="33"/>
+      <c r="E10" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="K10" s="33" t="s">
         <v>111</v>
       </c>
     </row>
@@ -12656,17 +12671,92 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="95237" r:id="rId4" name="_ActiveXWrapper4">
+        <control shapeId="95233" r:id="rId4" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>523875</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
                 <xdr:col>5</xdr:col>
+                <xdr:colOff>285750</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="95233" r:id="rId4" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="95234" r:id="rId6" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>419100</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>476250</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="95234" r:id="rId6" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="95235" r:id="rId8" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>504825</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>314325</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="95235" r:id="rId8" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="95237" r:id="rId10" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>581025</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>114300</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>6</xdr:col>
+                <xdr:col>7</xdr:col>
                 <xdr:colOff>752475</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
@@ -12676,82 +12766,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="95237" r:id="rId4" name="_ActiveXWrapper4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="95235" r:id="rId6" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>504825</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>314325</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="95235" r:id="rId6" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="95234" r:id="rId8" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>419100</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>476250</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="95234" r:id="rId8" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="95233" r:id="rId10" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>523875</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>285750</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>47625</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="95233" r:id="rId10" name="_ActiveXWrapper1"/>
+        <control shapeId="95237" r:id="rId10" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -12866,58 +12881,58 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="112641" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="112645" r:id="rId4" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>180975</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="112641" r:id="rId4" name="_ActiveXWrapper1"/>
+        <control shapeId="112645" r:id="rId4" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="112642" r:id="rId6" name="_ActiveXWrapper2">
+        <control shapeId="112644" r:id="rId6" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>85725</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
+                <xdr:rowOff>66675</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>171450</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>142875</xdr:rowOff>
+                <xdr:rowOff>133350</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="112642" r:id="rId6" name="_ActiveXWrapper2"/>
+        <control shapeId="112644" r:id="rId6" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
         <control shapeId="112643" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>3</xdr:col>
@@ -12941,52 +12956,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="112644" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+        <control shapeId="112642" r:id="rId9" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId10">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>85725</xdr:colOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>19050</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>171450</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>19050</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
+                <xdr:rowOff>142875</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="112644" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="112642" r:id="rId9" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="112645" r:id="rId11" name="_ActiveXWrapper5">
+        <control shapeId="112641" r:id="rId11" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId12">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>19050</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>180975</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>19050</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>104775</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="112645" r:id="rId11" name="_ActiveXWrapper5"/>
+        <control shapeId="112641" r:id="rId11" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -13113,8 +13128,83 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="113665" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="113669" r:id="rId4" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>771525</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="113669" r:id="rId4" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="113667" r:id="rId6" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1323975</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>971550</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="113667" r:id="rId6" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="113666" r:id="rId8" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1257300</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="113666" r:id="rId8" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="113665" r:id="rId10" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>3</xdr:col>
@@ -13133,82 +13223,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="113665" r:id="rId4" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="113666" r:id="rId6" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>9525</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1257300</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="113666" r:id="rId6" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="113667" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1323975</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>971550</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="113667" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="113669" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>771525</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="113669" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="113665" r:id="rId10" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -13373,52 +13388,52 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="37892" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="37896" r:id="rId4" name="_ActiveXWrapper5">
           <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>1019175</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>876300</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>104775</xdr:rowOff>
+                <xdr:rowOff>114300</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>714375</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>676275</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>123825</xdr:rowOff>
+                <xdr:rowOff>114300</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="37892" r:id="rId4" name="_ActiveXWrapper1"/>
+        <control shapeId="37896" r:id="rId4" name="_ActiveXWrapper5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="37893" r:id="rId6" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId7">
+        <control shapeId="37895" r:id="rId6" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>857250</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>771525</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>685800</xdr:colOff>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
+                <xdr:rowOff>19050</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="37893" r:id="rId6" name="_ActiveXWrapper2"/>
+        <control shapeId="37895" r:id="rId6" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -13448,52 +13463,52 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="37895" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+        <control shapeId="37893" r:id="rId10" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>771525</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>857250</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>161925</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>257175</xdr:colOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>685800</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
+                <xdr:rowOff>38100</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="37895" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="37893" r:id="rId10" name="_ActiveXWrapper2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="37896" r:id="rId12" name="_ActiveXWrapper5">
+        <control shapeId="37892" r:id="rId12" name="_ActiveXWrapper1">
           <controlPr defaultSize="0" autoLine="0" autoPict="0" r:id="rId13">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>876300</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>1019175</xdr:colOff>
                 <xdr:row>4</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
+                <xdr:rowOff>104775</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>676275</xdr:colOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>714375</xdr:colOff>
                 <xdr:row>7</xdr:row>
-                <xdr:rowOff>114300</xdr:rowOff>
+                <xdr:rowOff>123825</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="37896" r:id="rId12" name="_ActiveXWrapper5"/>
+        <control shapeId="37892" r:id="rId12" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -13648,8 +13663,83 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="28679" r:id="rId4" name="_ActiveXWrapper11">
+        <control shapeId="28678" r:id="rId4" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>266700</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>180975</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="28678" r:id="rId4" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="28677" r:id="rId6" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>295275</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>171450</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="28677" r:id="rId6" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="28676" r:id="rId8" name="_ActiveXWrapper5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>314325</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>142875</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="28676" r:id="rId8" name="_ActiveXWrapper5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="28679" r:id="rId10" name="_ActiveXWrapper11">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
@@ -13668,82 +13758,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="28679" r:id="rId4" name="_ActiveXWrapper11"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="28676" r:id="rId6" name="_ActiveXWrapper5">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>314325</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>47625</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>142875</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>28575</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="28676" r:id="rId6" name="_ActiveXWrapper5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="28677" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>295275</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>171450</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="28677" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="28678" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>266700</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>57150</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>180975</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="28678" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="28679" r:id="rId10" name="_ActiveXWrapper11"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -13812,8 +13827,83 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="10241" r:id="rId4" name="_ActiveXWrapper1">
+        <control shapeId="10244" r:id="rId4" name="_ActiveXWrapper4">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1219200</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>990600</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="10244" r:id="rId4" name="_ActiveXWrapper4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="10243" r:id="rId6" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1323975</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>1095375</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="10243" r:id="rId6" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="10242" r:id="rId8" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>19050</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>180975</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>1181100</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="10242" r:id="rId8" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="10241" r:id="rId10" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>4</xdr:col>
@@ -13832,82 +13922,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="10241" r:id="rId4" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="10242" r:id="rId6" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>19050</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1181100</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="10242" r:id="rId6" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="10243" r:id="rId8" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1323975</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1095375</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="10243" r:id="rId8" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="10244" r:id="rId10" name="_ActiveXWrapper4">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>1219200</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>180975</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>990600</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="10244" r:id="rId10" name="_ActiveXWrapper4"/>
+        <control shapeId="10241" r:id="rId10" name="_ActiveXWrapper1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -14117,8 +14132,133 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="81925" r:id="rId4" name="_ActiveXWrapper4">
+        <control shapeId="81927" r:id="rId4" name="_ActiveXWrapper6">
           <controlPr defaultSize="0" autoLine="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>590550</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>590550</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="81927" r:id="rId4" name="_ActiveXWrapper6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="81926" r:id="rId6" name="_ActiveXWrapper5">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>161925</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>457200</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="81926" r:id="rId6" name="_ActiveXWrapper5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="81921" r:id="rId8" name="_ActiveXWrapper1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>47625</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>1371600</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>95250</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="81921" r:id="rId8" name="_ActiveXWrapper1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="81922" r:id="rId10" name="_ActiveXWrapper2">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>104775</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>457200</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>152400</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="81922" r:id="rId10" name="_ActiveXWrapper2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="81923" r:id="rId12" name="_ActiveXWrapper3">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>38100</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>161925</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="81923" r:id="rId12" name="_ActiveXWrapper3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="81925" r:id="rId14" name="_ActiveXWrapper4">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>8</xdr:col>
@@ -14137,132 +14277,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="81925" r:id="rId4" name="_ActiveXWrapper4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="81923" r:id="rId6" name="_ActiveXWrapper3">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>38100</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>161925</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="81923" r:id="rId6" name="_ActiveXWrapper3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="81922" r:id="rId8" name="_ActiveXWrapper2">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>104775</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>457200</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="81922" r:id="rId8" name="_ActiveXWrapper2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="81921" r:id="rId10" name="_ActiveXWrapper1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId11">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>47625</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>76200</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>1371600</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>95250</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="81921" r:id="rId10" name="_ActiveXWrapper1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="81926" r:id="rId12" name="_ActiveXWrapper5">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId13">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>161925</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>457200</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="81926" r:id="rId12" name="_ActiveXWrapper5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="81927" r:id="rId14" name="_ActiveXWrapper6">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId15">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>590550</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>590550</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>85725</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="81927" r:id="rId14" name="_ActiveXWrapper6"/>
+        <control shapeId="81925" r:id="rId14" name="_ActiveXWrapper4"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
